--- a/packages/backend/test/preguntasDomain/helpers/practicas_20260406.xlsx
+++ b/packages/backend/test/preguntasDomain/helpers/practicas_20260406.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palonso\Documents\projects\preparaTAI\packages\backend\test\preguntasDomain\helpers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pablo\projects\preparaTAI\packages\backend\test\preguntasDomain\helpers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930FE339-8DC5-4E39-9E1D-9AF5D52628E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5A95EC-2EF4-44DE-85B3-A5E4100F37A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 9" sheetId="2" r:id="rId1"/>
@@ -19700,13 +19700,12 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="E212:G212"/>
-    <mergeCell ref="E206:H206"/>
-    <mergeCell ref="E207:F207"/>
-    <mergeCell ref="E208:H208"/>
-    <mergeCell ref="E209:G209"/>
-    <mergeCell ref="E210:F210"/>
-    <mergeCell ref="E211:H211"/>
+    <mergeCell ref="E193:G193"/>
+    <mergeCell ref="E188:F188"/>
+    <mergeCell ref="E189:G189"/>
+    <mergeCell ref="E190:G190"/>
+    <mergeCell ref="E191:F191"/>
+    <mergeCell ref="E192:F192"/>
     <mergeCell ref="E205:G205"/>
     <mergeCell ref="E194:G194"/>
     <mergeCell ref="E195:G195"/>
@@ -19719,12 +19718,13 @@
     <mergeCell ref="E202:F202"/>
     <mergeCell ref="E203:F203"/>
     <mergeCell ref="E204:G204"/>
-    <mergeCell ref="E193:G193"/>
-    <mergeCell ref="E188:F188"/>
-    <mergeCell ref="E189:G189"/>
-    <mergeCell ref="E190:G190"/>
-    <mergeCell ref="E191:F191"/>
-    <mergeCell ref="E192:F192"/>
+    <mergeCell ref="E212:G212"/>
+    <mergeCell ref="E206:H206"/>
+    <mergeCell ref="E207:F207"/>
+    <mergeCell ref="E208:H208"/>
+    <mergeCell ref="E209:G209"/>
+    <mergeCell ref="E210:F210"/>
+    <mergeCell ref="E211:H211"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D569" r:id="rId1" xr:uid="{7686DDD5-196C-4E91-9337-11240B52A089}"/>

--- a/packages/backend/test/preguntasDomain/helpers/practicas_20260406.xlsx
+++ b/packages/backend/test/preguntasDomain/helpers/practicas_20260406.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930FE339-8DC5-4E39-9E1D-9AF5D52628E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4500" yWindow="4140" windowWidth="21600" windowHeight="10335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 9" sheetId="2" r:id="rId1"/>
@@ -19700,13 +19700,12 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="E212:G212"/>
-    <mergeCell ref="E206:H206"/>
-    <mergeCell ref="E207:F207"/>
-    <mergeCell ref="E208:H208"/>
-    <mergeCell ref="E209:G209"/>
-    <mergeCell ref="E210:F210"/>
-    <mergeCell ref="E211:H211"/>
+    <mergeCell ref="E193:G193"/>
+    <mergeCell ref="E188:F188"/>
+    <mergeCell ref="E189:G189"/>
+    <mergeCell ref="E190:G190"/>
+    <mergeCell ref="E191:F191"/>
+    <mergeCell ref="E192:F192"/>
     <mergeCell ref="E205:G205"/>
     <mergeCell ref="E194:G194"/>
     <mergeCell ref="E195:G195"/>
@@ -19719,12 +19718,13 @@
     <mergeCell ref="E202:F202"/>
     <mergeCell ref="E203:F203"/>
     <mergeCell ref="E204:G204"/>
-    <mergeCell ref="E193:G193"/>
-    <mergeCell ref="E188:F188"/>
-    <mergeCell ref="E189:G189"/>
-    <mergeCell ref="E190:G190"/>
-    <mergeCell ref="E191:F191"/>
-    <mergeCell ref="E192:F192"/>
+    <mergeCell ref="E212:G212"/>
+    <mergeCell ref="E206:H206"/>
+    <mergeCell ref="E207:F207"/>
+    <mergeCell ref="E208:H208"/>
+    <mergeCell ref="E209:G209"/>
+    <mergeCell ref="E210:F210"/>
+    <mergeCell ref="E211:H211"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D569" r:id="rId1" xr:uid="{7686DDD5-196C-4E91-9337-11240B52A089}"/>
